--- a/consent_forms/050_horseback_riding_waiver--consent_forms.xlsx
+++ b/consent_forms/050_horseback_riding_waiver--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -934,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1817,46 +1817,46 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>horseback</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Horseback</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>rider_info_2_choices</t>
+          <t>emergency_contact_relation_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>horseback</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Horseback</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>rider_info_2_choices</t>
+          <t>emergency_contact_relation_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>horseback</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Horseback</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>mother</t>
+          <t>brother</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Brother</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>father</t>
+          <t>sister</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Sister</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>brother</t>
+          <t>wife</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Wife</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>sister</t>
+          <t>husband</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Husband</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>wife</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>husband</t>
+          <t>son</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Son</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>friend</t>
+          <t>daughter</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Daughter</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>son</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>daughter</t>
+          <t>son-in-law</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Son-in-law</t>
         </is>
       </c>
     </row>
@@ -2021,131 +2021,80 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>daughter-in-law</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Parent</t>
+          <t>Daughter-in-law</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>emergency_contact_relation_choices</t>
+          <t>emergency_contact_permission_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>son-in-law</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Son-in-law</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>emergency_contact_relation_choices</t>
+          <t>emergency_contact_permission_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>daughter-in-law</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Daughter-in-law</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>emergency_contact_permission_choices</t>
+          <t>rider_info_3_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>horseback</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Horseback</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>emergency_contact_permission_choices</t>
+          <t>rider_info_3_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>rider_info_3_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>horseback</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Horseback</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>rider_info_3_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>horseback</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Horseback</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>rider_info_3_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>horseback</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Horseback</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
